--- a/output/CLOTH01_summer/feeds_excel/master data feeds/ItemMasterGroup.xlsx
+++ b/output/CLOTH01_summer/feeds_excel/master data feeds/ItemMasterGroup.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ITM_BAS_0001</t>
+          <t>ITM_CHIPS_8OZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,94 +457,6 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>fast</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ITM_BAS_0002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>WOMENS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>BASICS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>fast</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ITM_TOP_0003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KIDS</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TOPS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ITM_TOP_0004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MENS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TOPS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ITM_BOT_0005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>WOMENS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>BOTTOMS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>slow</t>
         </is>
       </c>
     </row>
